--- a/Courses/Term 3/QAM-III/601 DATA Caps - Price Qty Cost profit.xlsx
+++ b/Courses/Term 3/QAM-III/601 DATA Caps - Price Qty Cost profit.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suranjandas/Desktop/SIRMAUR. IIM .. Nov 14 2025/T1 - Non Linear Programming/Data to students - Email/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B53793-64AD-A743-AB43-3CB52D4C966A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1076737D-8F77-594A-B147-D3BA723A1948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1760" yWindow="1320" windowWidth="27640" windowHeight="16760" xr2:uid="{B2BED8D6-8C7E-0E42-9D17-93C443EBC8CA}"/>
   </bookViews>
   <sheets>
     <sheet name="601 caps Exp()" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +27,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>The Selling Price for a monkey cap varies within the range of $5 to $20 based on Demand conditions driven by the weather and customer preference.</t>
   </si>
@@ -68,13 +69,28 @@
   <si>
     <t>What is the Price at which you will a) Maximize revenue b) Mamimize profit?</t>
   </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>PROFIT</t>
+  </si>
+  <si>
+    <t>COGS</t>
+  </si>
+  <si>
+    <t>DEMAND</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="8" formatCode="&quot;₹&quot;#,##0.00_);[Red]\(&quot;₹&quot;#,##0.00\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0.00_);[Red]\(&quot;₹&quot;#,##0.00\)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -127,7 +143,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -149,9 +165,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -189,7 +205,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -295,7 +311,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -437,7 +453,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -445,8 +461,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309BED9E-3E41-FF4D-B485-F8C73E39BF82}">
-  <dimension ref="A1:Q11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Q24"/>
+  <sheetFormatPr defaultColWidth="10.8515625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11.58984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.58984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -488,7 +508,7 @@
       <c r="L6" s="2"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="8" spans="1:17" ht="20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" ht="21" x14ac:dyDescent="0.2">
       <c r="C8" s="4" t="s">
         <v>4</v>
       </c>
@@ -496,6 +516,92 @@
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15">
+        <f>B13-B14</f>
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>496.58530380000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="F16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17">
+        <f>1000*EXP(-0.1*B13)</f>
+        <v>496.58530379140944</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F24">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Courses/Term 3/QAM-III/601 DATA Caps - Price Qty Cost profit.xlsx
+++ b/Courses/Term 3/QAM-III/601 DATA Caps - Price Qty Cost profit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suranjandas/Desktop/SIRMAUR. IIM .. Nov 14 2025/T1 - Non Linear Programming/Data to students - Email/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MBA\Courses\Term 3\QAM-III\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1076737D-8F77-594A-B147-D3BA723A1948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB5A1B6-7985-48AD-ADDB-E08B3E352CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="1320" windowWidth="27640" windowHeight="16760" xr2:uid="{B2BED8D6-8C7E-0E42-9D17-93C443EBC8CA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B2BED8D6-8C7E-0E42-9D17-93C443EBC8CA}"/>
   </bookViews>
   <sheets>
     <sheet name="601 caps Exp()" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>The Selling Price for a monkey cap varies within the range of $5 to $20 based on Demand conditions driven by the weather and customer preference.</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>QTY</t>
+  </si>
+  <si>
+    <t>REVENUE</t>
   </si>
 </sst>
 </file>
@@ -461,46 +464,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309BED9E-3E41-FF4D-B485-F8C73E39BF82}">
-  <dimension ref="A1:Q24"/>
-  <sheetFormatPr defaultColWidth="10.8515625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Q34"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.58984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.58984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="L2" s="2"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="L3" s="2"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="L4" s="2"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="L5" s="2"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -508,17 +512,17 @@
       <c r="L6" s="2"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="8" spans="1:17" ht="21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" ht="19.8" x14ac:dyDescent="0.3">
       <c r="C8" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -526,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -539,8 +543,11 @@
       <c r="G14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="H14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -549,15 +556,32 @@
         <v>2</v>
       </c>
       <c r="G15">
-        <v>496.58530380000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+        <f>1000*EXP(-0.1*B13)</f>
+        <v>496.58530379140944</v>
+      </c>
+      <c r="I15" t="str">
+        <f>IF(H15=MAX($H$15:$H$34),"Max Revenue","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="F16">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G16">
+        <f t="dataTable" ref="G16:G34" dt2D="0" dtr="0" r1="B13"/>
+        <v>818.73075307798183</v>
+      </c>
+      <c r="H16">
+        <f>G16*F16</f>
+        <v>1637.4615061559637</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" ref="I16:I34" si="0">IF(H16=MAX($H$15:$H$34),"Max Revenue","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -568,40 +592,288 @@
       <c r="F17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G17">
+        <v>740.81822068171789</v>
+      </c>
+      <c r="H17">
+        <f t="shared" ref="H17:H34" si="1">G17*F17</f>
+        <v>2222.4546620451538</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G18">
+        <v>670.32004603563928</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>2681.2801841425571</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F19">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G19">
+        <v>606.53065971263345</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>3032.6532985631675</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F20">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G20">
+        <v>548.81163609402643</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>3292.8698165641586</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F21">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G21">
+        <v>496.58530379140944</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>3476.0971265398662</v>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F22">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G22">
+        <v>449.32896411722157</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>3594.6317129377726</v>
+      </c>
+      <c r="I22" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F23">
         <v>9</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G23">
+        <v>406.56965974059909</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>3659.1269376653918</v>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F24">
         <v>10</v>
+      </c>
+      <c r="G24">
+        <v>367.87944117144235</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>3678.7944117144234</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="0"/>
+        <v>Max Revenue</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F25">
+        <v>11</v>
+      </c>
+      <c r="G25">
+        <v>332.87108369807953</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>3661.5819206788747</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F26">
+        <v>12</v>
+      </c>
+      <c r="G26">
+        <v>301.19421191220204</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>3614.3305429464244</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F27">
+        <v>13</v>
+      </c>
+      <c r="G27">
+        <v>272.53179303401259</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="1"/>
+        <v>3542.9133094421636</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F28">
+        <v>14</v>
+      </c>
+      <c r="G28">
+        <v>246.59696394160645</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="1"/>
+        <v>3452.3574951824903</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F29">
+        <v>15</v>
+      </c>
+      <c r="G29">
+        <v>223.13016014842981</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="1"/>
+        <v>3346.9524022264472</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F30">
+        <v>16</v>
+      </c>
+      <c r="G30">
+        <v>201.8965179946554</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="1"/>
+        <v>3230.3442879144864</v>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F31">
+        <v>17</v>
+      </c>
+      <c r="G31">
+        <v>182.68352405273461</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="1"/>
+        <v>3105.6199088964886</v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F32">
+        <v>18</v>
+      </c>
+      <c r="G32">
+        <v>165.29888822158654</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="1"/>
+        <v>2975.3799879885578</v>
+      </c>
+      <c r="I32" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F33">
+        <v>19</v>
+      </c>
+      <c r="G33">
+        <v>149.56861922263502</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="1"/>
+        <v>2841.8037652300654</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F34">
+        <v>20</v>
+      </c>
+      <c r="G34">
+        <v>135.3352832366127</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="1"/>
+        <v>2706.7056647322538</v>
+      </c>
+      <c r="I34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
   </sheetData>
